--- a/MavenBook/src/test/resources/Items.xlsx
+++ b/MavenBook/src/test/resources/Items.xlsx
@@ -64,9 +64,6 @@
     <t>Default</t>
   </si>
   <si>
-    <t>Box</t>
-  </si>
-  <si>
     <t>Selling Desc</t>
   </si>
   <si>
@@ -74,6 +71,9 @@
   </si>
   <si>
     <t>Pear</t>
+  </si>
+  <si>
+    <t>NOS</t>
   </si>
 </sst>
 </file>
@@ -487,7 +487,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2">
         <v>400</v>
@@ -505,28 +505,19 @@
         <v>123</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2">
+        <v>2000</v>
+      </c>
+      <c r="I2">
+        <v>1500</v>
+      </c>
+      <c r="J2" t="s">
         <v>16</v>
       </c>
-      <c r="H2">
-        <v>200</v>
-      </c>
-      <c r="I2">
-        <v>160</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>17</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2">
-        <v>10</v>
-      </c>
-      <c r="M2">
-        <v>160</v>
-      </c>
-      <c r="N2">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">

--- a/MavenBook/src/test/resources/Items.xlsx
+++ b/MavenBook/src/test/resources/Items.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -58,22 +58,19 @@
     <t>EAN Code</t>
   </si>
   <si>
-    <t>General</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
     <t>Selling Desc</t>
   </si>
   <si>
     <t>Pur Desc</t>
   </si>
   <si>
-    <t>Pear</t>
-  </si>
-  <si>
-    <t>NOS</t>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>KG</t>
   </si>
 </sst>
 </file>
@@ -487,25 +484,19 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C2">
         <v>401</v>
       </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
       <c r="F2">
         <v>123</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H2">
         <v>2000</v>
@@ -514,10 +505,51 @@
         <v>1500</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2">
+        <v>10</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>17</v>
+      </c>
+      <c r="B3">
+        <v>402</v>
+      </c>
+      <c r="C3">
+        <v>401</v>
+      </c>
+      <c r="F3">
+        <v>123</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3">
+        <v>1000</v>
+      </c>
+      <c r="I3">
+        <v>800</v>
+      </c>
+      <c r="J3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3">
+        <v>15</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
